--- a/Assets/test260903/chapter0204.xlsx
+++ b/Assets/test260903/chapter0204.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="256" documentId="11_E2BE8883BFC1EE042E83A027A8BF20BA6737391E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BD8A5F1-9039-4E94-8105-79E282C27CC0}"/>
+  <bookViews>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="chapter0204" sheetId="1" r:id="rId4"/>
+    <sheet name="chapter0204" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1wnk63aERf7/uTyT6okFjiq/Ayajw31Os+0y4XC6imY="/>
@@ -16,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="115">
   <si>
     <t>Command</t>
   </si>
@@ -76,27 +85,495 @@
   </si>
   <si>
     <t>*chapter0205_Start</t>
+  </si>
+  <si>
+    <t>背景：黒</t>
+    <rPh sb="3" eb="4">
+      <t>クロ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Se</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>走る足音</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>FadeIn</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>black</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>女は駆ける。少年の手を引いて</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>この街は、アジア最大の歓楽街で
+犯罪都市である</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>富が集まる土地の常、
+夢に敗れた貧困層たちが群れを作り……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>巨大なスラム街を形成していた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……嗅いだことのない悪臭がした。
+電柱に吊られた死体の匂いだった</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>主人公</t>
+    <rPh sb="0" eb="3">
+      <t>シュジンコウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>背景：スラム街</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>StopSe</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>走る足音</t>
+  </si>
+  <si>
+    <t>ふぅ……ここまで逃げれば大丈夫だよ。
+連中じゃ追いつけない</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>鈴野美鈴</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>通常</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ここがスラム街……
+噂には聞いていたけれど、酷い場所だ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ここは迷路みたいなもんだからさ。
+顔なじみ以外にとってはね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さんは相変わらず笑っている。
+けれど、笑える状態じゃない</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>僕も美鈴さんも裏切られた。
+美鈴さんは組織の後ろ盾を失ったんだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>顔色が悪いね？　熱中症？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Selection</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0204-1-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0204-1-b</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>バカ言ってる場合ですか！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>裏切られたんですよ！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Jump</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0204-1合流</t>
+    <rPh sb="10" eb="12">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>上等っ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>喜び</t>
+    <rPh sb="0" eb="1">
+      <t>ヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>え？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>上等上等♪
+これくらい厳しい相手じゃないとね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>私って強いからさ、
+ザコは相手にしたくないの</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あんたの叔父さん、
+そして私の所属する組織の白蛇……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>どっちも敵に回して、
+やっとトントンって感じかな♪</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>理解できない……
+この状況で、まだ勝算があるのか？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>さてっ！
+そんじゃ師匠のところに行こう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0204-2-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>師匠？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>うん。私に中国拳法と銃の使い方、
+あとは剣術、棒術……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ま、とにかく全てを教えてくれた人。
+その人がここの奥に住んでるの</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>変人だから、
+こういうところに住みたがるんだよね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……そして僕は、
+美鈴さんに連れられて街を進んだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>やがて崩れかけた、廃屋に辿り着くと、
+そこには1人の老人が立っていた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>師匠！　ご無沙汰～！！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……この人が、美鈴さんの師匠？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>歩く足音</t>
+  </si>
+  <si>
+    <t>……美鈴、相変わらず
+蛮勇ばかり振るっているようだのう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>師匠</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>通常</t>
+    <rPh sb="0" eb="2">
+      <t>ツウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>白蛇の人間から連絡があったわ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>お前が組織を裏切って逃げている。
+もし接触して来たら、殺してくれと</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ありゃ、マジで？
+師匠は何て答えたの？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>できるかい。子どもの頃ならまだしも、
+今のお前と戦ったら、わしが死ぬわ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ウッソだ～！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>殺すのは断っても、
+負けるとは思ってないよね？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>まぁな。わしは無敵じゃからのう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>しかし、白蛇はつまらん組織になったわ。
+子ども殺しの仕事を受けるとはのう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>早々に距離をとって正解じゃな。
+やっぱりわしは先見の明もあるわい</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>それ、逆だよ。師匠が抜けたから、
+組織がつまんなくなったの</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>今の白蛇の中心にいるのは、
+喧嘩もできない連中ばっかりだし</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>まったく……こりゃつまらんのう。
+喝を入れてやらんといかん</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>同感～♪</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>というわけで、白蛇の方は任せておけ。
+お前には武器を分けてやろう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>わしに武器をタカりにきたんじゃろ？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>正解！　さすがアタシの師匠！
+話が早い！！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>隣の廃屋が武器庫になっておる。
+好きなだけ持っていけ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>わしは古い仲間を集めて、
+白蛇の現執行陣と話をしてくるわ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>了解！
+師匠、よろしくお願いしまーす！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ヒヒヒ……久しぶりの修羅場じゃ。
+血が騒ぐのう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>気味の悪い笑い声を残して、
+美鈴さんの師匠は消えた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>&lt;Off&gt;</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さんと廃屋に入った。
+そこは確かに武器庫になっていて……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>扉を開ける</t>
+  </si>
+  <si>
+    <t>Bg</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>おおっ、さすが師匠～！
+充実の品ぞろえじゃん</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>拳銃に、ロケランに、手りゅう弾……
+この街の名物が全部揃ってる♪</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>おおっ！　対物ライフルまである！
+どこで手に入れたんだ、師匠！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>たしかに凄い量の武器だ。
+並の傭兵会社の金庫より凄い</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でも……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0204-3-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こっちは1人ですよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>平気だよ。
+アタシ、無敵だから</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>売られたケンカは買うもんだろ。
+どんなに割に合わないケンカでもさ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>怒り</t>
+    <rPh sb="0" eb="1">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>売られたケンカは買う。
+ムカついたら殴る</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そういうシンプルな感じで行こう。
+じゃないと、ストレスで死ぬよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>おっ！　車もあるじゃん！
+防弾仕様の黒ベンツだ！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>背景：武器庫</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>よし、装備の準備万端！
+エロガキ……！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>乗って！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>車のドア</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……無茶な戦いだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>背景：車内（ベンツ）</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,49 +581,65 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -336,28 +829,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L1070"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.5"/>
-    <col customWidth="1" min="2" max="2" width="14.0"/>
-    <col customWidth="1" min="3" max="7" width="5.13"/>
-    <col customWidth="1" min="8" max="8" width="8.63"/>
-    <col customWidth="1" min="9" max="9" width="37.75"/>
-    <col customWidth="1" min="10" max="10" width="8.25"/>
-    <col customWidth="1" min="11" max="11" width="6.0"/>
-    <col customWidth="1" min="12" max="12" width="11.38"/>
-    <col customWidth="1" min="13" max="26" width="8.0"/>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="7" width="5.109375" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="37.77734375" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="13" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:12" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -395,686 +888,1220 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="1"/>
       <c r="H2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1">
-      <c r="B6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="3" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" ht="13.5" customHeight="1">
+      <c r="B7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" ht="13.5" customHeight="1">
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-    </row>
-    <row r="9" ht="13.5" customHeight="1">
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" ht="13.5" customHeight="1">
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" ht="13.5" customHeight="1">
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" ht="13.5" customHeight="1">
-      <c r="I12" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" ht="13.5" customHeight="1">
+      <c r="I9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="28.2" customHeight="1">
+      <c r="I10" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="28.2" customHeight="1">
+      <c r="I11" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="13.5" customHeight="1">
+      <c r="I12" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="G13" s="1"/>
+    <row r="13" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+    <row r="14" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" ht="13.5" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+    <row r="15" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" ht="13.5" customHeight="1">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="I16" s="1"/>
+    <row r="16" spans="1:12" ht="30" customHeight="1">
+      <c r="B16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" ht="13.5" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" ht="13.5" customHeight="1">
+    <row r="17" spans="1:10" ht="30" customHeight="1">
+      <c r="B17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="30" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" ht="13.5" customHeight="1">
+      <c r="B18" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="I18" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" ht="28.8" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" ht="13.5" customHeight="1">
+      <c r="B19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" ht="28.8" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" ht="13.5" customHeight="1">
-      <c r="B21" s="1"/>
+      <c r="B20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="I20" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B21" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="C21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" ht="13.5" customHeight="1">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" ht="13.5" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" ht="13.5" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" ht="13.5" customHeight="1">
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
+      <c r="I21" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A22" s="1"/>
+      <c r="B22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A23" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A24" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" ht="13.5" customHeight="1">
-      <c r="B26" s="1"/>
+    <row r="26" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A26" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="C26" s="1"/>
       <c r="I26" s="1"/>
     </row>
-    <row r="27" ht="13.5" customHeight="1">
-      <c r="A27" s="1"/>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A27" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" ht="13.5" customHeight="1">
-      <c r="A28" s="1"/>
+    </row>
+    <row r="28" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A28" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" ht="13.5" customHeight="1">
+    <row r="29" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A29" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="I29" s="1"/>
-    </row>
-    <row r="30" ht="13.5" customHeight="1">
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" ht="13.5" customHeight="1">
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" ht="13.5" customHeight="1">
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" ht="13.5" customHeight="1">
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" ht="13.5" customHeight="1">
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" ht="13.5" customHeight="1">
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" ht="13.5" customHeight="1">
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" ht="13.5" customHeight="1">
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" ht="13.5" customHeight="1">
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" ht="13.5" customHeight="1">
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B30" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B31" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="I31" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A32" s="1"/>
+      <c r="B32" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" ht="30" customHeight="1">
+      <c r="A33" s="1"/>
+      <c r="B33" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="30" customHeight="1">
+      <c r="B34" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B35" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B36" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="30" customHeight="1">
+      <c r="B37" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A38" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A39" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="I39" s="1"/>
     </row>
-    <row r="40" ht="13.5" customHeight="1">
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" ht="13.5" customHeight="1">
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" ht="13.5" customHeight="1">
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" ht="13.5" customHeight="1">
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" ht="13.5" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-    </row>
-    <row r="47" ht="13.5" customHeight="1">
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="I47" s="1"/>
-    </row>
-    <row r="48" ht="13.5" customHeight="1">
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-    </row>
-    <row r="49" ht="13.5" customHeight="1">
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" ht="13.5" customHeight="1">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" ht="13.5" customHeight="1">
+    <row r="40" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B40" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B41" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B42" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A43" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="I43" s="8"/>
+    </row>
+    <row r="44" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B44" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="I44" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B45" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A46" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I46" s="8"/>
+    </row>
+    <row r="47" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B47" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B48" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B49" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B50" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="28.8" customHeight="1">
       <c r="A51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-    </row>
-    <row r="52" ht="13.5" customHeight="1">
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="I52" s="1"/>
-    </row>
-    <row r="53" ht="13.5" customHeight="1">
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="I53" s="1"/>
-    </row>
-    <row r="54" ht="13.5" customHeight="1">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="I54" s="1"/>
-    </row>
-    <row r="55" ht="13.5" customHeight="1">
-      <c r="A55" s="1"/>
-      <c r="I55" s="1"/>
-    </row>
-    <row r="56" ht="13.5" customHeight="1">
-      <c r="I56" s="1"/>
-    </row>
-    <row r="57" ht="13.5" customHeight="1">
-      <c r="I57" s="1"/>
-    </row>
-    <row r="58" ht="13.5" customHeight="1">
+      <c r="B51" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A52" s="1"/>
+      <c r="B52" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A53" s="1"/>
+      <c r="B53" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B54" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="30" customHeight="1">
+      <c r="B55" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B56" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="1:10" ht="30" customHeight="1">
+      <c r="A57" s="1"/>
+      <c r="B57" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" ht="28.2" customHeight="1">
       <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="I58" s="1"/>
-    </row>
-    <row r="59" ht="13.5" customHeight="1">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="I59" s="1"/>
-    </row>
-    <row r="60" ht="13.5" customHeight="1">
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="I60" s="1"/>
-    </row>
-    <row r="61" ht="13.5" customHeight="1">
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="I61" s="1"/>
-    </row>
-    <row r="62" ht="13.5" customHeight="1">
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="I62" s="1"/>
-    </row>
-    <row r="63" ht="13.5" customHeight="1">
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="I63" s="1"/>
-    </row>
-    <row r="64" ht="13.5" customHeight="1">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" ht="13.5" customHeight="1">
+      <c r="B58" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B59" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="30" customHeight="1">
+      <c r="B60" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A61" s="1"/>
+      <c r="B61" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A62" s="1"/>
+      <c r="B62" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="30" customHeight="1">
+      <c r="B63" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B64" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="28.8" customHeight="1">
       <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" ht="13.5" customHeight="1">
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="I66" s="1"/>
-    </row>
-    <row r="67" ht="13.5" customHeight="1">
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="I67" s="1"/>
-    </row>
-    <row r="68" ht="13.5" customHeight="1">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="I68" s="1"/>
-    </row>
-    <row r="69" ht="13.5" customHeight="1">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-    </row>
-    <row r="70" ht="13.5" customHeight="1">
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="I70" s="1"/>
-    </row>
-    <row r="71" ht="13.5" customHeight="1">
-      <c r="B71" s="1"/>
+      <c r="B65" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A66" s="1"/>
+      <c r="B66" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B67" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B68" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B69" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B70" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I70" s="8"/>
+    </row>
+    <row r="71" spans="1:9" ht="31.2" customHeight="1">
+      <c r="B71" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="C71" s="1"/>
-      <c r="I71" s="1"/>
-    </row>
-    <row r="72" ht="13.5" customHeight="1">
-      <c r="B72" s="1"/>
+      <c r="I71" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="31.2" customHeight="1">
+      <c r="A72" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>94</v>
+      </c>
       <c r="C72" s="1"/>
-      <c r="I72" s="1"/>
-    </row>
-    <row r="73" ht="13.5" customHeight="1">
-      <c r="B73" s="1"/>
+      <c r="I72" s="8"/>
+    </row>
+    <row r="73" spans="1:9" ht="31.2" customHeight="1">
+      <c r="A73" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>109</v>
+      </c>
       <c r="C73" s="1"/>
-      <c r="I73" s="1"/>
-    </row>
-    <row r="74" ht="13.5" customHeight="1">
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="I74" s="1"/>
-    </row>
-    <row r="75" ht="13.5" customHeight="1">
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="I75" s="1"/>
-    </row>
-    <row r="76" ht="13.5" customHeight="1">
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="I76" s="1"/>
-    </row>
-    <row r="77" ht="13.5" customHeight="1">
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="I77" s="1"/>
-    </row>
-    <row r="78" ht="13.5" customHeight="1">
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-    </row>
-    <row r="79" ht="13.5" customHeight="1">
-      <c r="I79" s="1"/>
-    </row>
-    <row r="80" ht="13.5" customHeight="1">
-      <c r="I80" s="1"/>
-    </row>
-    <row r="81" ht="13.5" customHeight="1">
+      <c r="I73" s="8"/>
+    </row>
+    <row r="74" spans="1:9" ht="30" customHeight="1">
+      <c r="A74" s="1"/>
+      <c r="B74" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="31.8" customHeight="1">
+      <c r="A75" s="1"/>
+      <c r="B75" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H75" s="1"/>
+      <c r="I75" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B76" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="30" customHeight="1">
+      <c r="B77" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="27.6" customHeight="1">
+      <c r="A78" s="1"/>
+      <c r="B78" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C78" s="7"/>
+      <c r="I78" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A79" s="1"/>
+      <c r="B79" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H79" s="1"/>
+      <c r="I79" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A80" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="I80" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A81" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
       <c r="I81" s="1"/>
     </row>
-    <row r="82" ht="13.5" customHeight="1">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-    </row>
-    <row r="83" ht="13.5" customHeight="1">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-    </row>
-    <row r="84" ht="13.5" customHeight="1">
-      <c r="A84" s="1"/>
-    </row>
-    <row r="85" ht="13.5" customHeight="1">
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="I85" s="1"/>
-    </row>
-    <row r="86" ht="13.5" customHeight="1">
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="I86" s="1"/>
-    </row>
-    <row r="87" ht="13.5" customHeight="1">
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="I87" s="1"/>
-    </row>
-    <row r="88" ht="13.5" customHeight="1">
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="I88" s="1"/>
-    </row>
-    <row r="89" ht="13.5" customHeight="1">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-    </row>
-    <row r="90" ht="13.5" customHeight="1">
-      <c r="A90" s="1"/>
-    </row>
-    <row r="91" ht="13.5" customHeight="1">
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="I91" s="1"/>
-    </row>
-    <row r="92" ht="13.5" customHeight="1">
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
+    <row r="82" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B82" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="30" customHeight="1">
+      <c r="B83" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B84" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B85" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B86" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B87" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A88" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C88" s="7"/>
+      <c r="I88" s="8"/>
+    </row>
+    <row r="89" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B89" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="J89" s="1"/>
+    </row>
+    <row r="90" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A90" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C90" s="7"/>
+      <c r="I90" s="8"/>
+      <c r="J90" s="1"/>
+    </row>
+    <row r="91" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B91" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="13.5" customHeight="1">
       <c r="I92" s="1"/>
     </row>
-    <row r="93" ht="13.5" customHeight="1">
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
+    <row r="93" spans="1:10" ht="13.5" customHeight="1">
       <c r="I93" s="1"/>
     </row>
-    <row r="94" ht="13.5" customHeight="1">
+    <row r="94" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A94" s="1"/>
       <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
       <c r="I94" s="1"/>
-    </row>
-    <row r="95" ht="13.5" customHeight="1">
+      <c r="J94" s="1"/>
+    </row>
+    <row r="95" spans="1:10" ht="13.5" customHeight="1">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
-    </row>
-    <row r="96" ht="13.5" customHeight="1">
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+    </row>
+    <row r="96" spans="1:10" ht="13.5" customHeight="1">
       <c r="A96" s="1"/>
     </row>
-    <row r="97" ht="13.5" customHeight="1">
+    <row r="97" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
       <c r="I97" s="1"/>
     </row>
-    <row r="98" ht="13.5" customHeight="1">
+    <row r="98" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
       <c r="I98" s="1"/>
     </row>
-    <row r="99" ht="13.5" customHeight="1">
-      <c r="A99" s="1"/>
+    <row r="99" spans="1:9" ht="13.5" customHeight="1">
       <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
       <c r="I99" s="1"/>
     </row>
-    <row r="100" ht="13.5" customHeight="1">
-      <c r="A100" s="1"/>
-      <c r="H100" s="1"/>
+    <row r="100" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
       <c r="I100" s="1"/>
     </row>
-    <row r="101" ht="13.5" customHeight="1">
+    <row r="101" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A101" s="1"/>
       <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-      <c r="I101" s="1"/>
-    </row>
-    <row r="102" ht="13.5" customHeight="1">
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-      <c r="I102" s="1"/>
-    </row>
-    <row r="103" ht="13.5" customHeight="1">
+    </row>
+    <row r="102" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A102" s="1"/>
+    </row>
+    <row r="103" spans="1:9" ht="13.5" customHeight="1">
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
       <c r="I103" s="1"/>
     </row>
-    <row r="104" ht="13.5" customHeight="1">
+    <row r="104" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
       <c r="I104" s="1"/>
     </row>
-    <row r="105" ht="13.5" customHeight="1">
+    <row r="105" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
       <c r="I105" s="1"/>
     </row>
-    <row r="106" ht="13.5" customHeight="1">
+    <row r="106" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
       <c r="I106" s="1"/>
     </row>
-    <row r="107" ht="13.5" customHeight="1">
-      <c r="I107" s="1"/>
-    </row>
-    <row r="108" ht="13.5" customHeight="1">
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="I108" s="1"/>
-    </row>
-    <row r="109" ht="13.5" customHeight="1">
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
+    <row r="107" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
+    </row>
+    <row r="108" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A108" s="1"/>
+    </row>
+    <row r="109" spans="1:9" ht="13.5" customHeight="1">
       <c r="I109" s="1"/>
     </row>
-    <row r="110" ht="13.5" customHeight="1">
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
+    <row r="110" spans="1:9" ht="13.5" customHeight="1">
       <c r="I110" s="1"/>
     </row>
-    <row r="111" ht="13.5" customHeight="1">
+    <row r="111" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A111" s="1"/>
       <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
       <c r="I111" s="1"/>
     </row>
-    <row r="112" ht="13.5" customHeight="1">
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
+    <row r="112" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A112" s="1"/>
+      <c r="H112" s="1"/>
       <c r="I112" s="1"/>
     </row>
-    <row r="113" ht="13.5" customHeight="1">
-      <c r="A113" s="1"/>
+    <row r="113" spans="1:10" ht="13.5" customHeight="1">
       <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
       <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
-    </row>
-    <row r="114" ht="13.5" customHeight="1">
-      <c r="A114" s="1"/>
+    </row>
+    <row r="114" spans="1:10" ht="13.5" customHeight="1">
       <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
       <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
-    </row>
-    <row r="115" ht="13.5" customHeight="1">
-      <c r="A115" s="1"/>
+    </row>
+    <row r="115" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
       <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
-    </row>
-    <row r="116" ht="13.5" customHeight="1">
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
+    </row>
+    <row r="116" spans="1:10" ht="13.5" customHeight="1">
       <c r="I116" s="1"/>
     </row>
-    <row r="117" ht="13.5" customHeight="1">
-      <c r="A117" s="1"/>
-      <c r="B117" s="1"/>
-    </row>
-    <row r="118" ht="13.5" customHeight="1">
-      <c r="A118" s="1"/>
-    </row>
-    <row r="119" ht="13.5" customHeight="1">
-      <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
+    <row r="117" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I117" s="1"/>
+    </row>
+    <row r="118" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I118" s="1"/>
+    </row>
+    <row r="119" spans="1:10" ht="13.5" customHeight="1">
       <c r="I119" s="1"/>
     </row>
-    <row r="120" ht="13.5" customHeight="1">
+    <row r="120" spans="1:10" ht="13.5" customHeight="1">
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
       <c r="I120" s="1"/>
     </row>
-    <row r="121" ht="13.5" customHeight="1">
+    <row r="121" spans="1:10" ht="13.5" customHeight="1">
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
       <c r="I121" s="1"/>
     </row>
-    <row r="122" ht="13.5" customHeight="1">
-      <c r="A122" s="1"/>
+    <row r="122" spans="1:10" ht="13.5" customHeight="1">
       <c r="B122" s="1"/>
-    </row>
-    <row r="123" ht="13.5" customHeight="1">
-      <c r="A123" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="I122" s="1"/>
+    </row>
+    <row r="123" spans="1:10" ht="13.5" customHeight="1">
       <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
       <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
-    </row>
-    <row r="124" ht="13.5" customHeight="1">
+    </row>
+    <row r="124" spans="1:10" ht="13.5" customHeight="1">
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
       <c r="I124" s="1"/>
     </row>
-    <row r="125" ht="13.5" customHeight="1">
+    <row r="125" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A125" s="1"/>
       <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
       <c r="I125" s="1"/>
-    </row>
-    <row r="126" ht="13.5" customHeight="1">
+      <c r="J125" s="1"/>
+    </row>
+    <row r="126" spans="1:10" ht="13.5" customHeight="1">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
-    </row>
-    <row r="127" ht="13.5" customHeight="1">
+      <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
+    </row>
+    <row r="127" spans="1:10" ht="13.5" customHeight="1">
       <c r="A127" s="1"/>
-    </row>
-    <row r="128" ht="13.5" customHeight="1">
+      <c r="I127" s="1"/>
+      <c r="J127" s="1"/>
+    </row>
+    <row r="128" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
       <c r="I128" s="1"/>
     </row>
-    <row r="129" ht="13.5" customHeight="1">
+    <row r="129" spans="1:10" ht="13.5" customHeight="1">
       <c r="A129" s="1"/>
-    </row>
-    <row r="130" ht="13.5" customHeight="1">
+      <c r="B129" s="1"/>
+    </row>
+    <row r="130" spans="1:10" ht="13.5" customHeight="1">
       <c r="A130" s="1"/>
     </row>
-    <row r="131" ht="13.5" customHeight="1">
-      <c r="A131" s="1"/>
+    <row r="131" spans="1:10" ht="13.5" customHeight="1">
       <c r="B131" s="1"/>
-      <c r="H131" s="1"/>
+      <c r="C131" s="1"/>
       <c r="I131" s="1"/>
     </row>
-    <row r="132" ht="13.5" customHeight="1">
-      <c r="A132" s="1"/>
-      <c r="H132" s="1"/>
+    <row r="132" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
       <c r="I132" s="1"/>
     </row>
-    <row r="133" ht="13.5" customHeight="1">
+    <row r="133" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
       <c r="I133" s="1"/>
     </row>
-    <row r="134" ht="13.5" customHeight="1">
-      <c r="I134" s="1"/>
-    </row>
-    <row r="135" ht="13.5" customHeight="1">
+    <row r="134" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A134" s="1"/>
+      <c r="B134" s="1"/>
+    </row>
+    <row r="135" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A135" s="1"/>
+      <c r="B135" s="1"/>
       <c r="I135" s="1"/>
-    </row>
-    <row r="136" ht="13.5" customHeight="1">
+      <c r="J135" s="1"/>
+    </row>
+    <row r="136" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
       <c r="I136" s="1"/>
     </row>
-    <row r="137" ht="13.5" customHeight="1">
+    <row r="137" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
       <c r="I137" s="1"/>
     </row>
-    <row r="138" ht="13.5" customHeight="1">
-      <c r="I138" s="1"/>
-    </row>
-    <row r="139" ht="13.5" customHeight="1">
-      <c r="I139" s="1"/>
-    </row>
-    <row r="140" ht="13.5" customHeight="1"/>
-    <row r="141" ht="13.5" customHeight="1"/>
-    <row r="142" ht="13.5" customHeight="1"/>
-    <row r="143" ht="13.5" customHeight="1"/>
-    <row r="144" ht="13.5" customHeight="1"/>
-    <row r="145" ht="13.5" customHeight="1"/>
-    <row r="146" ht="13.5" customHeight="1"/>
-    <row r="147" ht="13.5" customHeight="1"/>
-    <row r="148" ht="13.5" customHeight="1"/>
-    <row r="149" ht="13.5" customHeight="1"/>
-    <row r="150" ht="13.5" customHeight="1"/>
-    <row r="151" ht="13.5" customHeight="1"/>
-    <row r="152" ht="13.5" customHeight="1"/>
-    <row r="153" ht="13.5" customHeight="1"/>
-    <row r="154" ht="13.5" customHeight="1"/>
-    <row r="155" ht="13.5" customHeight="1"/>
-    <row r="156" ht="13.5" customHeight="1"/>
-    <row r="157" ht="13.5" customHeight="1"/>
-    <row r="158" ht="13.5" customHeight="1"/>
-    <row r="159" ht="13.5" customHeight="1"/>
-    <row r="160" ht="13.5" customHeight="1"/>
+    <row r="138" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A138" s="1"/>
+      <c r="B138" s="1"/>
+    </row>
+    <row r="139" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A139" s="1"/>
+    </row>
+    <row r="140" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I140" s="1"/>
+    </row>
+    <row r="141" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A141" s="1"/>
+    </row>
+    <row r="142" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A142" s="1"/>
+    </row>
+    <row r="143" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A143" s="1"/>
+      <c r="B143" s="1"/>
+      <c r="H143" s="1"/>
+      <c r="I143" s="1"/>
+    </row>
+    <row r="144" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A144" s="1"/>
+      <c r="H144" s="1"/>
+      <c r="I144" s="1"/>
+    </row>
+    <row r="145" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I145" s="1"/>
+    </row>
+    <row r="146" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I146" s="1"/>
+    </row>
+    <row r="147" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I147" s="1"/>
+    </row>
+    <row r="148" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I148" s="1"/>
+    </row>
+    <row r="149" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I149" s="1"/>
+    </row>
+    <row r="150" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I150" s="1"/>
+    </row>
+    <row r="151" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I151" s="1"/>
+    </row>
+    <row r="152" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="153" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="154" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="155" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="156" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="157" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="158" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="159" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="160" spans="9:9" ht="13.5" customHeight="1"/>
     <row r="161" ht="13.5" customHeight="1"/>
     <row r="162" ht="13.5" customHeight="1"/>
     <row r="163" ht="13.5" customHeight="1"/>
@@ -1107,22 +2134,29 @@
     <row r="190" ht="13.5" customHeight="1"/>
     <row r="191" ht="13.5" customHeight="1"/>
     <row r="192" ht="13.5" customHeight="1"/>
-    <row r="193" ht="13.5" customHeight="1"/>
-    <row r="194" ht="13.5" customHeight="1"/>
-    <row r="195" ht="13.5" customHeight="1"/>
-    <row r="196" ht="13.5" customHeight="1"/>
-    <row r="197" ht="13.5" customHeight="1"/>
-    <row r="198" ht="13.5" customHeight="1"/>
-    <row r="199" ht="13.5" customHeight="1"/>
-    <row r="200" ht="13.5" customHeight="1"/>
-    <row r="201" ht="13.5" customHeight="1"/>
-    <row r="202" ht="13.5" customHeight="1"/>
-    <row r="203" ht="13.5" customHeight="1"/>
-    <row r="204" ht="13.5" customHeight="1"/>
-    <row r="205" ht="13.5" customHeight="1"/>
-    <row r="206" ht="13.5" customHeight="1"/>
-    <row r="207" ht="13.5" customHeight="1"/>
-    <row r="208" ht="13.5" customHeight="1"/>
+    <row r="193" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="194" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="195" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="196" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="197" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="198" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="199" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="200" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="201" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="202" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="203" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A203" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="205" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="206" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="207" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="208" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="209" ht="13.5" customHeight="1"/>
     <row r="210" ht="13.5" customHeight="1"/>
     <row r="211" ht="13.5" customHeight="1"/>
@@ -1973,10 +3007,21 @@
     <row r="1056" ht="13.5" customHeight="1"/>
     <row r="1057" ht="13.5" customHeight="1"/>
     <row r="1058" ht="13.5" customHeight="1"/>
+    <row r="1059" ht="13.5" customHeight="1"/>
+    <row r="1060" ht="13.5" customHeight="1"/>
+    <row r="1061" ht="13.5" customHeight="1"/>
+    <row r="1062" ht="13.5" customHeight="1"/>
+    <row r="1063" ht="13.5" customHeight="1"/>
+    <row r="1064" ht="13.5" customHeight="1"/>
+    <row r="1065" ht="13.5" customHeight="1"/>
+    <row r="1066" ht="13.5" customHeight="1"/>
+    <row r="1067" ht="13.5" customHeight="1"/>
+    <row r="1068" ht="13.5" customHeight="1"/>
+    <row r="1069" ht="13.5" customHeight="1"/>
+    <row r="1070" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/test260903/chapter0204.xlsx
+++ b/Assets/test260903/chapter0204.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="11_E2BE8883BFC1EE042E83A027A8BF20BA6737391E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BD8A5F1-9039-4E94-8105-79E282C27CC0}"/>
+  <xr:revisionPtr revIDLastSave="402" documentId="11_E2BE8883BFC1EE042E83A027A8BF20BA6737391E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E17B526-15DE-4158-8539-EA1F256B420E}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="162">
   <si>
     <t>Command</t>
   </si>
@@ -526,6 +526,212 @@
   </si>
   <si>
     <t>背景：車内（ベンツ）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さんは強い。
+それは間違いないとは思う</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でもこれは、そういう問題じゃない。
+いくら美鈴さんが強いからと言って……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>敵は僕の身内であり、
+美鈴さんの身内でもある</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こっちの手は知られている。
+それに僕は、僕の組織の怖さも知っている</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>お～～い、エロガキ～～！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>父さんも叔父も、恐ろしい人物だ。
+敵に回したくはない</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こうやって、家族すら切るヤツら……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>イテ……！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>殴打（ゲンコツ）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Shake</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Camera</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>x=3.</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>だから、無視すんなっての！
+礼儀がなってない！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>何か聞かれたら、すぐ答える！
+これ基本だから！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あんた、いっつも難しい顔して、
+あれこれ考えているっぽいけど……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あんたを殺そうとしてるヤツがいる。
+なのに、何を考えるわけ？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……言われてみればそうだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>僕は今、殺されそうなんだ。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>相手が誰だろうと
+勝てる可能性が低かろうと……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>考えている場合じゃない……！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0204-4-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>行きます！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>よし！　それでいい！！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さんは車をブッ飛ばした。
+走らせるでもなく、ブッ飛ばしたんだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>背景：黒</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>車の走行（急発進）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>急カーブに最高速度で突っ込み、
+何度も車をあちこちにブツけた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こんなものは「運転」とか、言えない
+「走らせた」なんていえない</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そして僕が２～３回ほど吐くと……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>車は、叔父の会社の正面玄関が見えてきた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>おっ！　正面に部隊を配置してある！
+土嚢を積んで、機関銃もか！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>正面突破を想定してる配備！
+私の性格をよく分かってるなぁ！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>上等っ♪</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>まさか正面から行く気ですか？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0204-5-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>もちろん！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0204-6-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>やっぱり～！？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>打死你！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……次の瞬間、</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>銃撃戦（連射）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>完全防弾の黒ベンツは、
+銃撃を受けながら正面玄関に突撃</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>車の衝突</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>x=10.</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>正面の見張りを跳ね飛ばしながら、
+車は会社のエントランスに侵入し</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>少年を背負った女が、車から飛び出し
+銃撃戦へ突入した</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>FadeOut</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -596,7 +802,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -617,6 +823,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -836,14 +1045,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1070"/>
+  <dimension ref="A1:L1082"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="7" width="5.109375" customWidth="1"/>
     <col min="8" max="8" width="8.6640625" customWidth="1"/>
-    <col min="9" max="9" width="37.77734375" customWidth="1"/>
+    <col min="9" max="9" width="39.44140625" customWidth="1"/>
     <col min="10" max="10" width="8.21875" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
     <col min="12" max="12" width="11.33203125" customWidth="1"/>
@@ -1838,286 +2047,597 @@
         <v>113</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I92" s="1"/>
-    </row>
-    <row r="93" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I93" s="1"/>
-    </row>
-    <row r="94" spans="1:10" ht="13.5" customHeight="1">
+    <row r="92" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B92" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B93" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="28.8" customHeight="1">
       <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="I94" s="1"/>
+      <c r="B94" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>117</v>
+      </c>
       <c r="J94" s="1"/>
     </row>
-    <row r="95" spans="1:10" ht="13.5" customHeight="1">
+    <row r="95" spans="1:10" ht="28.8" customHeight="1">
       <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-      <c r="I95" s="1"/>
+      <c r="B95" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>118</v>
+      </c>
       <c r="J95" s="1"/>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1">
       <c r="A96" s="1"/>
-    </row>
-    <row r="97" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B97" s="1"/>
+      <c r="B96" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B97" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="C97" s="1"/>
-      <c r="I97" s="1"/>
+      <c r="I97" s="8" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="98" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B98" s="1"/>
+      <c r="B98" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="C98" s="1"/>
-      <c r="I98" s="1"/>
+      <c r="I98" s="8" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="99" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="I99" s="1"/>
+      <c r="A99" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I99" s="8"/>
     </row>
     <row r="100" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B100" s="1"/>
+      <c r="A100" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>125</v>
+      </c>
       <c r="C100" s="1"/>
-      <c r="I100" s="1"/>
-    </row>
-    <row r="101" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A101" s="1"/>
-      <c r="B101" s="1"/>
-    </row>
-    <row r="102" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A102" s="1"/>
-    </row>
-    <row r="103" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="I103" s="1"/>
-    </row>
-    <row r="104" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="I104" s="1"/>
-    </row>
-    <row r="105" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B105" s="1"/>
-      <c r="C105" s="1"/>
-      <c r="I105" s="1"/>
+      <c r="D100" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="I100" s="8"/>
+    </row>
+    <row r="101" spans="1:9" ht="13.2" customHeight="1">
+      <c r="B101" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C101" s="1"/>
+      <c r="I101" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B102" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B103" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I103" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="30" customHeight="1">
+      <c r="A104" s="1"/>
+      <c r="B104" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I104" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B105" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I105" s="8" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="106" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B106" s="1"/>
+      <c r="B106" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="C106" s="1"/>
-      <c r="I106" s="1"/>
+      <c r="I106" s="8" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="107" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A107" s="1"/>
-      <c r="B107" s="1"/>
-    </row>
-    <row r="108" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A108" s="1"/>
+      <c r="B107" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C107" s="1"/>
+      <c r="I107" s="8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B108" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C108" s="1"/>
+      <c r="I108" s="8" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="109" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I109" s="1"/>
+      <c r="A109" s="1"/>
+      <c r="B109" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="110" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I110" s="1"/>
+      <c r="A110" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="111" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A111" s="1"/>
-      <c r="B111" s="1"/>
+      <c r="A111" s="1" t="s">
+        <v>135</v>
+      </c>
       <c r="I111" s="1"/>
     </row>
     <row r="112" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A112" s="1"/>
-      <c r="H112" s="1"/>
-      <c r="I112" s="1"/>
-    </row>
-    <row r="113" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
-      <c r="I113" s="1"/>
-    </row>
-    <row r="114" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
-      <c r="I114" s="1"/>
-    </row>
-    <row r="115" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
-      <c r="I115" s="1"/>
-    </row>
-    <row r="116" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I116" s="1"/>
-    </row>
-    <row r="117" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I117" s="1"/>
-    </row>
-    <row r="118" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I118" s="1"/>
-    </row>
-    <row r="119" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I119" s="1"/>
-    </row>
-    <row r="120" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B120" s="1"/>
+      <c r="B112" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A113" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C113" s="9"/>
+      <c r="I113" s="8"/>
+    </row>
+    <row r="114" spans="1:9" ht="13.2" customHeight="1">
+      <c r="A114" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C114" s="9"/>
+      <c r="I114" s="8"/>
+    </row>
+    <row r="115" spans="1:9" ht="13.2" customHeight="1">
+      <c r="A115" s="5"/>
+      <c r="B115" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I115" s="8"/>
+    </row>
+    <row r="116" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A116" s="1"/>
+      <c r="B116" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A117" s="1"/>
+      <c r="B117" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H117" s="1"/>
+      <c r="I117" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B118" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C118" s="1"/>
+      <c r="I118" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B119" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C119" s="1"/>
+      <c r="I119" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B120" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="C120" s="1"/>
-      <c r="I120" s="1"/>
-    </row>
-    <row r="121" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B121" s="1"/>
+      <c r="I120" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A121" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="C121" s="1"/>
-      <c r="I121" s="1"/>
-    </row>
-    <row r="122" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="I122" s="1"/>
-    </row>
-    <row r="123" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
-      <c r="I123" s="1"/>
-    </row>
-    <row r="124" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="I124" s="1"/>
-    </row>
-    <row r="125" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A125" s="1"/>
-      <c r="B125" s="1"/>
-      <c r="I125" s="1"/>
-      <c r="J125" s="1"/>
-    </row>
-    <row r="126" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A126" s="1"/>
+      <c r="I121" s="8"/>
+    </row>
+    <row r="122" spans="1:9" ht="30" customHeight="1">
+      <c r="B122" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="30" customHeight="1">
+      <c r="B123" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B124" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A125" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A126" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
       <c r="I126" s="1"/>
-      <c r="J126" s="1"/>
-    </row>
-    <row r="127" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A127" s="1"/>
-      <c r="I127" s="1"/>
-      <c r="J127" s="1"/>
-    </row>
-    <row r="128" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B128" s="1"/>
+    </row>
+    <row r="127" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B127" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A128" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>151</v>
+      </c>
       <c r="C128" s="1"/>
-      <c r="I128" s="1"/>
+      <c r="I128" s="8" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="129" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A129" s="1"/>
+      <c r="A129" s="1" t="s">
+        <v>151</v>
+      </c>
       <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="I129" s="1"/>
     </row>
     <row r="130" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A130" s="1"/>
+      <c r="B130" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="131" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="I131" s="1"/>
+      <c r="A131" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C131" s="6"/>
+      <c r="I131" s="8"/>
     </row>
     <row r="132" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B132" s="1"/>
-      <c r="C132" s="1"/>
-      <c r="I132" s="1"/>
+      <c r="A132" s="7"/>
+      <c r="B132" s="6"/>
+      <c r="C132" s="6"/>
+      <c r="I132" s="8"/>
     </row>
     <row r="133" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B133" s="1"/>
-      <c r="C133" s="1"/>
-      <c r="I133" s="1"/>
+      <c r="A133" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C133" s="6"/>
+      <c r="I133" s="8"/>
     </row>
     <row r="134" spans="1:10" ht="13.5" customHeight="1">
       <c r="A134" s="1"/>
-      <c r="B134" s="1"/>
+      <c r="B134" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I134" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="J134" s="1"/>
     </row>
     <row r="135" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A135" s="1"/>
-      <c r="B135" s="1"/>
-      <c r="I135" s="1"/>
+      <c r="A135" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="I135" s="8"/>
       <c r="J135" s="1"/>
     </row>
     <row r="136" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B136" s="1"/>
+      <c r="A136" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>125</v>
+      </c>
       <c r="C136" s="1"/>
-      <c r="I136" s="1"/>
-    </row>
-    <row r="137" spans="1:10" ht="13.5" customHeight="1">
+      <c r="D136" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="I136" s="8"/>
+      <c r="J136" s="1"/>
+    </row>
+    <row r="137" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A137" s="1"/>
       <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
-      <c r="I137" s="1"/>
-    </row>
-    <row r="138" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I137" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J137" s="1"/>
+    </row>
+    <row r="138" spans="1:10" ht="30" customHeight="1">
       <c r="A138" s="1"/>
-      <c r="B138" s="1"/>
-    </row>
-    <row r="139" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A139" s="1"/>
-    </row>
-    <row r="140" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I140" s="1"/>
+      <c r="I138" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="J138" s="1"/>
+    </row>
+    <row r="139" spans="1:10" ht="30" customHeight="1">
+      <c r="A139" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="I139" s="8"/>
+      <c r="J139" s="1"/>
+    </row>
+    <row r="140" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="I140" s="8" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="141" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A141" s="1"/>
+      <c r="A141" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G141">
+        <v>1</v>
+      </c>
     </row>
     <row r="142" spans="1:10" ht="13.5" customHeight="1">
       <c r="A142" s="1"/>
     </row>
     <row r="143" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A143" s="1"/>
       <c r="B143" s="1"/>
-      <c r="H143" s="1"/>
+      <c r="C143" s="1"/>
       <c r="I143" s="1"/>
     </row>
     <row r="144" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A144" s="1"/>
-      <c r="H144" s="1"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
       <c r="I144" s="1"/>
     </row>
-    <row r="145" spans="9:9" ht="13.5" customHeight="1">
+    <row r="145" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
       <c r="I145" s="1"/>
     </row>
-    <row r="146" spans="9:9" ht="13.5" customHeight="1">
-      <c r="I146" s="1"/>
-    </row>
-    <row r="147" spans="9:9" ht="13.5" customHeight="1">
+    <row r="146" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A146" s="1"/>
+      <c r="B146" s="1"/>
+    </row>
+    <row r="147" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A147" s="1"/>
+      <c r="B147" s="1"/>
       <c r="I147" s="1"/>
-    </row>
-    <row r="148" spans="9:9" ht="13.5" customHeight="1">
+      <c r="J147" s="1"/>
+    </row>
+    <row r="148" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
       <c r="I148" s="1"/>
     </row>
-    <row r="149" spans="9:9" ht="13.5" customHeight="1">
+    <row r="149" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
       <c r="I149" s="1"/>
     </row>
-    <row r="150" spans="9:9" ht="13.5" customHeight="1">
-      <c r="I150" s="1"/>
-    </row>
-    <row r="151" spans="9:9" ht="13.5" customHeight="1">
-      <c r="I151" s="1"/>
-    </row>
-    <row r="152" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="153" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="154" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="155" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="156" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="157" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="158" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="159" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="160" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="161" ht="13.5" customHeight="1"/>
-    <row r="162" ht="13.5" customHeight="1"/>
-    <row r="163" ht="13.5" customHeight="1"/>
-    <row r="164" ht="13.5" customHeight="1"/>
-    <row r="165" ht="13.5" customHeight="1"/>
-    <row r="166" ht="13.5" customHeight="1"/>
-    <row r="167" ht="13.5" customHeight="1"/>
-    <row r="168" ht="13.5" customHeight="1"/>
-    <row r="169" ht="13.5" customHeight="1"/>
-    <row r="170" ht="13.5" customHeight="1"/>
-    <row r="171" ht="13.5" customHeight="1"/>
-    <row r="172" ht="13.5" customHeight="1"/>
-    <row r="173" ht="13.5" customHeight="1"/>
-    <row r="174" ht="13.5" customHeight="1"/>
-    <row r="175" ht="13.5" customHeight="1"/>
-    <row r="176" ht="13.5" customHeight="1"/>
+    <row r="150" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A150" s="1"/>
+      <c r="B150" s="1"/>
+    </row>
+    <row r="151" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A151" s="1"/>
+    </row>
+    <row r="152" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I152" s="1"/>
+    </row>
+    <row r="153" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A153" s="1"/>
+    </row>
+    <row r="154" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A154" s="1"/>
+    </row>
+    <row r="155" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A155" s="1"/>
+      <c r="B155" s="1"/>
+      <c r="H155" s="1"/>
+      <c r="I155" s="1"/>
+    </row>
+    <row r="156" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A156" s="1"/>
+      <c r="H156" s="1"/>
+      <c r="I156" s="1"/>
+    </row>
+    <row r="157" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I157" s="1"/>
+    </row>
+    <row r="158" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I158" s="1"/>
+    </row>
+    <row r="159" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I159" s="1"/>
+    </row>
+    <row r="160" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I160" s="1"/>
+    </row>
+    <row r="161" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I161" s="1"/>
+    </row>
+    <row r="162" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I162" s="1"/>
+    </row>
+    <row r="163" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I163" s="1"/>
+    </row>
+    <row r="164" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="165" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="166" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="167" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="168" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="169" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="170" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="171" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="172" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="173" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="174" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="175" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="176" spans="9:9" ht="13.5" customHeight="1"/>
     <row r="177" ht="13.5" customHeight="1"/>
     <row r="178" ht="13.5" customHeight="1"/>
     <row r="179" ht="13.5" customHeight="1"/>
@@ -2134,45 +2654,45 @@
     <row r="190" ht="13.5" customHeight="1"/>
     <row r="191" ht="13.5" customHeight="1"/>
     <row r="192" ht="13.5" customHeight="1"/>
-    <row r="193" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="194" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="195" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="196" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="197" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="198" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="199" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="200" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="201" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="202" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="203" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A203" s="1" t="s">
+    <row r="193" ht="13.5" customHeight="1"/>
+    <row r="194" ht="13.5" customHeight="1"/>
+    <row r="195" ht="13.5" customHeight="1"/>
+    <row r="196" ht="13.5" customHeight="1"/>
+    <row r="197" ht="13.5" customHeight="1"/>
+    <row r="198" ht="13.5" customHeight="1"/>
+    <row r="199" ht="13.5" customHeight="1"/>
+    <row r="200" ht="13.5" customHeight="1"/>
+    <row r="201" ht="13.5" customHeight="1"/>
+    <row r="202" ht="13.5" customHeight="1"/>
+    <row r="203" ht="13.5" customHeight="1"/>
+    <row r="204" ht="13.5" customHeight="1"/>
+    <row r="205" ht="13.5" customHeight="1"/>
+    <row r="206" ht="13.5" customHeight="1"/>
+    <row r="207" ht="13.5" customHeight="1"/>
+    <row r="208" ht="13.5" customHeight="1"/>
+    <row r="209" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="210" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="211" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="212" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="213" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="214" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="215" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A215" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="B215" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="204" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="205" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="206" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="207" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="208" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="209" ht="13.5" customHeight="1"/>
-    <row r="210" ht="13.5" customHeight="1"/>
-    <row r="211" ht="13.5" customHeight="1"/>
-    <row r="212" ht="13.5" customHeight="1"/>
-    <row r="213" ht="13.5" customHeight="1"/>
-    <row r="214" ht="13.5" customHeight="1"/>
-    <row r="215" ht="13.5" customHeight="1"/>
-    <row r="216" ht="13.5" customHeight="1"/>
-    <row r="217" ht="13.5" customHeight="1"/>
-    <row r="218" ht="13.5" customHeight="1"/>
-    <row r="219" ht="13.5" customHeight="1"/>
-    <row r="220" ht="13.5" customHeight="1"/>
-    <row r="221" ht="13.5" customHeight="1"/>
-    <row r="222" ht="13.5" customHeight="1"/>
-    <row r="223" ht="13.5" customHeight="1"/>
-    <row r="224" ht="13.5" customHeight="1"/>
+    <row r="216" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="217" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="218" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="219" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="220" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="221" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="222" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="223" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="224" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="225" ht="13.5" customHeight="1"/>
     <row r="226" ht="13.5" customHeight="1"/>
     <row r="227" ht="13.5" customHeight="1"/>
@@ -3019,6 +3539,18 @@
     <row r="1068" ht="13.5" customHeight="1"/>
     <row r="1069" ht="13.5" customHeight="1"/>
     <row r="1070" ht="13.5" customHeight="1"/>
+    <row r="1071" ht="13.5" customHeight="1"/>
+    <row r="1072" ht="13.5" customHeight="1"/>
+    <row r="1073" ht="13.5" customHeight="1"/>
+    <row r="1074" ht="13.5" customHeight="1"/>
+    <row r="1075" ht="13.5" customHeight="1"/>
+    <row r="1076" ht="13.5" customHeight="1"/>
+    <row r="1077" ht="13.5" customHeight="1"/>
+    <row r="1078" ht="13.5" customHeight="1"/>
+    <row r="1079" ht="13.5" customHeight="1"/>
+    <row r="1080" ht="13.5" customHeight="1"/>
+    <row r="1081" ht="13.5" customHeight="1"/>
+    <row r="1082" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Assets/test260903/chapter0204.xlsx
+++ b/Assets/test260903/chapter0204.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="402" documentId="11_E2BE8883BFC1EE042E83A027A8BF20BA6737391E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E17B526-15DE-4158-8539-EA1F256B420E}"/>
+  <xr:revisionPtr revIDLastSave="407" documentId="11_E2BE8883BFC1EE042E83A027A8BF20BA6737391E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A3F0703-0367-4C79-8E51-9534D91076D7}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="163">
   <si>
     <t>Command</t>
   </si>
@@ -732,6 +732,10 @@
   </si>
   <si>
     <t>FadeOut</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>急ブレーキ（タイヤ音）</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1045,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1082"/>
+  <dimension ref="A1:L1084"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -2293,75 +2297,75 @@
       </c>
     </row>
     <row r="117" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A117" s="1"/>
+      <c r="A117" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="B117" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H117" s="1"/>
-      <c r="I117" s="8" t="s">
-        <v>141</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="I117" s="8"/>
     </row>
     <row r="118" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B118" s="6" t="s">
-        <v>30</v>
+      <c r="A118" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="C118" s="1"/>
-      <c r="I118" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" ht="13.5" customHeight="1">
+      <c r="D118" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="I118" s="8"/>
+    </row>
+    <row r="119" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A119" s="1"/>
       <c r="B119" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C119" s="1"/>
+      <c r="H119" s="1"/>
       <c r="I119" s="8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" ht="13.5" customHeight="1">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="28.8" customHeight="1">
       <c r="B120" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C120" s="1"/>
       <c r="I120" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B121" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C121" s="1"/>
+      <c r="I121" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B122" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C122" s="1"/>
+      <c r="I122" s="8" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A121" s="7" t="s">
+    <row r="123" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A123" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B121" s="6" t="s">
+      <c r="B123" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="C121" s="1"/>
-      <c r="I121" s="8"/>
-    </row>
-    <row r="122" spans="1:9" ht="30" customHeight="1">
-      <c r="B122" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I122" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" ht="30" customHeight="1">
-      <c r="B123" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C123" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I123" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="13.5" customHeight="1">
+      <c r="C123" s="1"/>
+      <c r="I123" s="8"/>
+    </row>
+    <row r="124" spans="1:9" ht="30" customHeight="1">
       <c r="B124" s="6" t="s">
         <v>35</v>
       </c>
@@ -2369,188 +2373,200 @@
         <v>50</v>
       </c>
       <c r="I124" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="30" customHeight="1">
+      <c r="B125" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B126" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I126" s="8" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A125" s="9" t="s">
+    <row r="127" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A127" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B127" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I125" s="8" t="s">
+      <c r="I127" s="8" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A126" s="1" t="s">
+    <row r="128" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A128" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="I126" s="1"/>
-    </row>
-    <row r="127" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B127" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C127" s="6" t="s">
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="I128" s="1"/>
+    </row>
+    <row r="129" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B129" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C129" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I127" s="8" t="s">
+      <c r="I129" s="8" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A128" s="9" t="s">
+    <row r="130" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A130" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B130" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C128" s="1"/>
-      <c r="I128" s="8" t="s">
+      <c r="C130" s="1"/>
+      <c r="I130" s="8" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A129" s="1" t="s">
+    <row r="131" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A131" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
-      <c r="I129" s="1"/>
-    </row>
-    <row r="130" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B130" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C130" s="6" t="s">
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="I131" s="1"/>
+    </row>
+    <row r="132" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B132" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C132" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I130" s="8" t="s">
+      <c r="I132" s="8" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A131" s="7" t="s">
+    <row r="133" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A133" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B131" s="6" t="s">
+      <c r="B133" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="C131" s="6"/>
-      <c r="I131" s="8"/>
-    </row>
-    <row r="132" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A132" s="7"/>
-      <c r="B132" s="6"/>
-      <c r="C132" s="6"/>
-      <c r="I132" s="8"/>
-    </row>
-    <row r="133" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A133" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="C133" s="6"/>
       <c r="I133" s="8"/>
     </row>
     <row r="134" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A134" s="1"/>
-      <c r="B134" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="I134" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="J134" s="1"/>
+      <c r="A134" s="7"/>
+      <c r="B134" s="6"/>
+      <c r="C134" s="6"/>
+      <c r="I134" s="8"/>
     </row>
     <row r="135" spans="1:10" ht="13.5" customHeight="1">
       <c r="A135" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B135" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C135" s="6"/>
+      <c r="I135" s="8"/>
+    </row>
+    <row r="136" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A136" s="1"/>
+      <c r="B136" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I136" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="J136" s="1"/>
+    </row>
+    <row r="137" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A137" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B137" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="I135" s="8"/>
-      <c r="J135" s="1"/>
-    </row>
-    <row r="136" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A136" s="6" t="s">
+      <c r="I137" s="8"/>
+      <c r="J137" s="1"/>
+    </row>
+    <row r="138" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A138" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B136" s="7" t="s">
+      <c r="B138" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C136" s="1"/>
-      <c r="D136" s="6" t="s">
+      <c r="C138" s="1"/>
+      <c r="D138" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="I136" s="8"/>
-      <c r="J136" s="1"/>
-    </row>
-    <row r="137" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A137" s="1"/>
-      <c r="B137" s="1"/>
-      <c r="I137" s="8" t="s">
+      <c r="I138" s="8"/>
+      <c r="J138" s="1"/>
+    </row>
+    <row r="139" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A139" s="1"/>
+      <c r="B139" s="1"/>
+      <c r="I139" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="J137" s="1"/>
-    </row>
-    <row r="138" spans="1:10" ht="30" customHeight="1">
-      <c r="A138" s="1"/>
-      <c r="I138" s="8" t="s">
+      <c r="J139" s="1"/>
+    </row>
+    <row r="140" spans="1:10" ht="30" customHeight="1">
+      <c r="A140" s="1"/>
+      <c r="I140" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="J138" s="1"/>
-    </row>
-    <row r="139" spans="1:10" ht="30" customHeight="1">
-      <c r="A139" s="5" t="s">
+      <c r="J140" s="1"/>
+    </row>
+    <row r="141" spans="1:10" ht="30" customHeight="1">
+      <c r="A141" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B139" s="6" t="s">
+      <c r="B141" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="I139" s="8"/>
-      <c r="J139" s="1"/>
-    </row>
-    <row r="140" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B140" s="1"/>
-      <c r="C140" s="1"/>
-      <c r="I140" s="8" t="s">
+      <c r="I141" s="8"/>
+      <c r="J141" s="1"/>
+    </row>
+    <row r="142" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
+      <c r="I142" s="8" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A141" s="7" t="s">
+    <row r="143" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A143" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B141" s="7" t="s">
+      <c r="B143" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G141">
+      <c r="G143">
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A142" s="1"/>
-    </row>
-    <row r="143" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B143" s="1"/>
-      <c r="C143" s="1"/>
-      <c r="I143" s="1"/>
-    </row>
     <row r="144" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B144" s="1"/>
-      <c r="C144" s="1"/>
-      <c r="I144" s="1"/>
+      <c r="A144" s="1"/>
     </row>
     <row r="145" spans="1:10" ht="13.5" customHeight="1">
       <c r="B145" s="1"/>
@@ -2558,56 +2574,60 @@
       <c r="I145" s="1"/>
     </row>
     <row r="146" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A146" s="1"/>
       <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
+      <c r="I146" s="1"/>
     </row>
     <row r="147" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A147" s="1"/>
       <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
       <c r="I147" s="1"/>
-      <c r="J147" s="1"/>
     </row>
     <row r="148" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A148" s="1"/>
       <c r="B148" s="1"/>
-      <c r="C148" s="1"/>
-      <c r="I148" s="1"/>
     </row>
     <row r="149" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A149" s="1"/>
       <c r="B149" s="1"/>
-      <c r="C149" s="1"/>
       <c r="I149" s="1"/>
+      <c r="J149" s="1"/>
     </row>
     <row r="150" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A150" s="1"/>
       <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
+      <c r="I150" s="1"/>
     </row>
     <row r="151" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A151" s="1"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
+      <c r="I151" s="1"/>
     </row>
     <row r="152" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I152" s="1"/>
+      <c r="A152" s="1"/>
+      <c r="B152" s="1"/>
     </row>
     <row r="153" spans="1:10" ht="13.5" customHeight="1">
       <c r="A153" s="1"/>
     </row>
     <row r="154" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A154" s="1"/>
+      <c r="I154" s="1"/>
     </row>
     <row r="155" spans="1:10" ht="13.5" customHeight="1">
       <c r="A155" s="1"/>
-      <c r="B155" s="1"/>
-      <c r="H155" s="1"/>
-      <c r="I155" s="1"/>
     </row>
     <row r="156" spans="1:10" ht="13.5" customHeight="1">
       <c r="A156" s="1"/>
-      <c r="H156" s="1"/>
-      <c r="I156" s="1"/>
     </row>
     <row r="157" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A157" s="1"/>
+      <c r="B157" s="1"/>
+      <c r="H157" s="1"/>
       <c r="I157" s="1"/>
     </row>
     <row r="158" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A158" s="1"/>
+      <c r="H158" s="1"/>
       <c r="I158" s="1"/>
     </row>
     <row r="159" spans="1:10" ht="13.5" customHeight="1">
@@ -2625,8 +2645,12 @@
     <row r="163" spans="9:9" ht="13.5" customHeight="1">
       <c r="I163" s="1"/>
     </row>
-    <row r="164" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="165" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="164" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I164" s="1"/>
+    </row>
+    <row r="165" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I165" s="1"/>
+    </row>
     <row r="166" spans="9:9" ht="13.5" customHeight="1"/>
     <row r="167" spans="9:9" ht="13.5" customHeight="1"/>
     <row r="168" spans="9:9" ht="13.5" customHeight="1"/>
@@ -2676,16 +2700,16 @@
     <row r="212" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="213" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="214" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="215" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A215" s="1" t="s">
+    <row r="215" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="216" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="217" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A217" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="B217" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="216" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="217" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="218" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="219" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="220" spans="1:2" ht="13.5" customHeight="1"/>
@@ -3551,6 +3575,8 @@
     <row r="1080" ht="13.5" customHeight="1"/>
     <row r="1081" ht="13.5" customHeight="1"/>
     <row r="1082" ht="13.5" customHeight="1"/>
+    <row r="1083" ht="13.5" customHeight="1"/>
+    <row r="1084" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Assets/test260903/chapter0204.xlsx
+++ b/Assets/test260903/chapter0204.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="407" documentId="11_E2BE8883BFC1EE042E83A027A8BF20BA6737391E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A3F0703-0367-4C79-8E51-9534D91076D7}"/>
+  <xr:revisionPtr revIDLastSave="423" documentId="11_E2BE8883BFC1EE042E83A027A8BF20BA6737391E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C8AC61F-B2FD-4DAB-A5C8-970A226144F4}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="168">
   <si>
     <t>Command</t>
   </si>
@@ -736,6 +736,26 @@
   </si>
   <si>
     <t>急ブレーキ（タイヤ音）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BGM_スラム</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Bgm</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>StopBgm</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BGM_バトル</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BGM_日常コミカル</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1049,7 +1069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1084"/>
+  <dimension ref="A1:L1089"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -1190,66 +1210,69 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:12" ht="13.5" customHeight="1">
-      <c r="I9" s="1" t="s">
+      <c r="A9" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" ht="13.5" customHeight="1">
+      <c r="I10" s="1" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="28.2" customHeight="1">
-      <c r="I10" s="8" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="28.2" customHeight="1">
       <c r="I11" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="28.2" customHeight="1">
+      <c r="I12" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="13.5" customHeight="1">
-      <c r="I12" s="1" t="s">
+    <row r="13" spans="1:12" ht="13.5" customHeight="1">
+      <c r="I13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:12" ht="13.5" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>33</v>
+        <v>24</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>31</v>
+      <c r="A15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:12" ht="30" customHeight="1">
-      <c r="B16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>29</v>
-      </c>
+    <row r="16" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10" ht="30" customHeight="1">
@@ -1257,25 +1280,20 @@
         <v>30</v>
       </c>
       <c r="I17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="30" customHeight="1">
+      <c r="B18" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" ht="30" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="I18" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="28.8" customHeight="1">
+    <row r="19" spans="1:10" ht="30" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="6" t="s">
         <v>35</v>
@@ -1283,53 +1301,56 @@
       <c r="C19" s="7" t="s">
         <v>36</v>
       </c>
+      <c r="G19" s="1"/>
       <c r="I19" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" ht="28.8" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="I20" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10" ht="28.2" customHeight="1">
+    <row r="21" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A21" s="1"/>
       <c r="B21" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="1"/>
       <c r="I21" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="I22" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A23" s="1"/>
+      <c r="B23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I23" s="8" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A23" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1">
@@ -1337,88 +1358,86 @@
         <v>42</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A25" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I25" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A25" s="1" t="s">
+    <row r="26" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A26" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A26" s="9" t="s">
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A27" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A29" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A29" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>48</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B30" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="A30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1">
       <c r="B31" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B32" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="1"/>
-      <c r="I31" s="1" t="s">
+      <c r="C32" s="1"/>
+      <c r="I32" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A32" s="1"/>
-      <c r="B32" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="1:10" ht="30" customHeight="1">
+    <row r="33" spans="1:10" ht="30.6" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="6" t="s">
         <v>35</v>
@@ -1427,11 +1446,12 @@
         <v>50</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="1:10" ht="30" customHeight="1">
+      <c r="A34" s="1"/>
       <c r="B34" s="6" t="s">
         <v>35</v>
       </c>
@@ -1439,10 +1459,11 @@
         <v>50</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="28.8" customHeight="1">
+        <v>53</v>
+      </c>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" ht="30" customHeight="1">
       <c r="B35" s="6" t="s">
         <v>35</v>
       </c>
@@ -1450,57 +1471,57 @@
         <v>50</v>
       </c>
       <c r="I35" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B36" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I36" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B36" s="6" t="s">
+    <row r="37" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B37" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I36" s="8" t="s">
+      <c r="I37" s="8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="30" customHeight="1">
-      <c r="B37" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="7" t="s">
+    <row r="38" spans="1:10" ht="30" customHeight="1">
+      <c r="B38" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="I37" s="8" t="s">
+      <c r="I38" s="8" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A38" s="9" t="s">
+    <row r="39" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A39" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="I39" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A39" s="1" t="s">
+    <row r="40" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A40" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="1:10" ht="27.6" customHeight="1">
-      <c r="B40" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="28.8" customHeight="1">
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="1:10" ht="27.6" customHeight="1">
       <c r="B41" s="6" t="s">
         <v>35</v>
       </c>
@@ -1508,7 +1529,7 @@
         <v>36</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="28.8" customHeight="1">
@@ -1519,135 +1540,135 @@
         <v>36</v>
       </c>
       <c r="I42" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B43" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A43" s="5" t="s">
+    <row r="44" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A44" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B44" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="7"/>
-      <c r="I43" s="8"/>
-    </row>
-    <row r="44" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B44" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C44" s="1"/>
-      <c r="I44" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="28.8" customHeight="1">
+      <c r="C44" s="7"/>
+      <c r="I44" s="8"/>
+    </row>
+    <row r="45" spans="1:10" ht="28.2" customHeight="1">
       <c r="B45" s="6" t="s">
         <v>30</v>
       </c>
+      <c r="C45" s="1"/>
       <c r="I45" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B46" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I46" s="8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A46" s="6" t="s">
+    <row r="47" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A47" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B47" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="I46" s="8"/>
-    </row>
-    <row r="47" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B47" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>65</v>
-      </c>
+      <c r="I47" s="8"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" customHeight="1">
       <c r="B48" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B49" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I48" s="8" t="s">
+      <c r="I49" s="8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B49" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="13.5" customHeight="1">
+    <row r="50" spans="1:10" ht="28.2" customHeight="1">
       <c r="B50" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C50" s="6" t="s">
         <v>70</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A51" s="1"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="13.5" customHeight="1">
       <c r="B51" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="9" t="s">
         <v>70</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="28.2" customHeight="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="28.8" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>36</v>
+        <v>69</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="28.2" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A54" s="1"/>
+      <c r="B54" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C54" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="I53" s="8" t="s">
+      <c r="I54" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="J53" s="1"/>
-    </row>
-    <row r="54" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B54" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="30" customHeight="1">
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="1:10" ht="13.5" customHeight="1">
       <c r="B55" s="6" t="s">
         <v>35</v>
       </c>
@@ -1655,24 +1676,22 @@
         <v>50</v>
       </c>
       <c r="I55" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="30" customHeight="1">
+      <c r="B56" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I56" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J55" s="1"/>
-    </row>
-    <row r="56" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B56" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I56" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="J56" s="1"/>
     </row>
-    <row r="57" spans="1:10" ht="30" customHeight="1">
-      <c r="A57" s="1"/>
+    <row r="57" spans="1:10" ht="13.5" customHeight="1">
       <c r="B57" s="6" t="s">
         <v>69</v>
       </c>
@@ -1680,11 +1699,11 @@
         <v>70</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="1:10" ht="28.2" customHeight="1">
+    <row r="58" spans="1:10" ht="30" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="6" t="s">
         <v>69</v>
@@ -1693,22 +1712,24 @@
         <v>70</v>
       </c>
       <c r="I58" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A59" s="1"/>
+      <c r="B59" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I59" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="J58" s="1"/>
-    </row>
-    <row r="59" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B59" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I59" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="30" customHeight="1">
+      <c r="J59" s="1"/>
+    </row>
+    <row r="60" spans="1:10" ht="28.2" customHeight="1">
       <c r="B60" s="6" t="s">
         <v>35</v>
       </c>
@@ -1716,45 +1737,45 @@
         <v>36</v>
       </c>
       <c r="I60" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="30" customHeight="1">
+      <c r="B61" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I61" s="8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A61" s="1"/>
-      <c r="B61" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I61" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="13.5" customHeight="1">
+    <row r="62" spans="1:10" ht="28.8" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C62" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A63" s="1"/>
+      <c r="B63" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C63" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="I62" s="8" t="s">
+      <c r="I63" s="8" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="30" customHeight="1">
-      <c r="B63" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I63" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="13.5" customHeight="1">
+    <row r="64" spans="1:10" ht="30" customHeight="1">
       <c r="B64" s="6" t="s">
         <v>69</v>
       </c>
@@ -1762,34 +1783,34 @@
         <v>70</v>
       </c>
       <c r="I64" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B65" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I65" s="8" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A65" s="1"/>
-      <c r="B65" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I65" s="8" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="28.8" customHeight="1">
       <c r="A66" s="1"/>
       <c r="B66" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>70</v>
+        <v>35</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="30.6" customHeight="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A67" s="1"/>
       <c r="B67" s="6" t="s">
         <v>69</v>
       </c>
@@ -1797,29 +1818,29 @@
         <v>70</v>
       </c>
       <c r="I67" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B68" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I68" s="8" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B68" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I68" s="8" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="28.8" customHeight="1">
       <c r="B69" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>70</v>
+        <v>35</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="28.8" customHeight="1">
@@ -1827,176 +1848,174 @@
         <v>69</v>
       </c>
       <c r="C70" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B71" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C71" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="I70" s="8"/>
-    </row>
-    <row r="71" spans="1:9" ht="31.2" customHeight="1">
-      <c r="B71" s="6" t="s">
+      <c r="I71" s="8"/>
+    </row>
+    <row r="72" spans="1:9" ht="31.2" customHeight="1">
+      <c r="B72" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C71" s="1"/>
-      <c r="I71" s="8" t="s">
+      <c r="C72" s="1"/>
+      <c r="I72" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="31.2" customHeight="1">
-      <c r="A72" s="5" t="s">
+    <row r="73" spans="1:9" ht="31.2" customHeight="1">
+      <c r="A73" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B73" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="I72" s="8"/>
-    </row>
-    <row r="73" spans="1:9" ht="31.2" customHeight="1">
-      <c r="A73" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="C73" s="1"/>
       <c r="I73" s="8"/>
     </row>
-    <row r="74" spans="1:9" ht="30" customHeight="1">
-      <c r="A74" s="1"/>
+    <row r="74" spans="1:9" ht="31.2" customHeight="1">
+      <c r="A74" s="7" t="s">
+        <v>95</v>
+      </c>
       <c r="B74" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I74" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="31.8" customHeight="1">
+        <v>109</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="I74" s="8"/>
+    </row>
+    <row r="75" spans="1:9" ht="30" customHeight="1">
       <c r="A75" s="1"/>
       <c r="B75" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="H75" s="1"/>
+        <v>30</v>
+      </c>
       <c r="I75" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B76" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I76" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="30" customHeight="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="30" customHeight="1">
+      <c r="A76" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I76" s="8"/>
+    </row>
+    <row r="77" spans="1:9" ht="31.8" customHeight="1">
+      <c r="A77" s="1"/>
       <c r="B77" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>50</v>
       </c>
+      <c r="H77" s="1"/>
       <c r="I77" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B78" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="30" customHeight="1">
+      <c r="B79" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I79" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="27.6" customHeight="1">
-      <c r="A78" s="1"/>
-      <c r="B78" s="6" t="s">
+    <row r="80" spans="1:9" ht="27.6" customHeight="1">
+      <c r="A80" s="1"/>
+      <c r="B80" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="I78" s="8" t="s">
+      <c r="C80" s="7"/>
+      <c r="I80" s="8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A79" s="1"/>
-      <c r="B79" s="6" t="s">
+    <row r="81" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A81" s="1"/>
+      <c r="B81" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H79" s="1"/>
-      <c r="I79" s="8" t="s">
+      <c r="H81" s="1"/>
+      <c r="I81" s="8" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A80" s="9" t="s">
+    <row r="82" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A82" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C80" s="1"/>
-      <c r="I80" s="8" t="s">
+      <c r="C82" s="1"/>
+      <c r="I82" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A81" s="1" t="s">
+    <row r="83" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A83" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="I81" s="1"/>
-    </row>
-    <row r="82" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B82" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I82" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="30" customHeight="1">
-      <c r="B83" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="I83" s="8" t="s">
-        <v>104</v>
-      </c>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="I83" s="1"/>
     </row>
     <row r="84" spans="1:10" ht="28.8" customHeight="1">
       <c r="B84" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C84" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="30" customHeight="1">
+      <c r="B85" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C85" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="I84" s="8" t="s">
+      <c r="I85" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B86" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I86" s="8" t="s">
         <v>106</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B85" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I85" s="8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B86" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I86" s="8" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="28.8" customHeight="1">
@@ -2007,20 +2026,21 @@
         <v>50</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A88" s="5" t="s">
-        <v>21</v>
-      </c>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="28.2" customHeight="1">
       <c r="B88" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C88" s="7"/>
-      <c r="I88" s="8"/>
-    </row>
-    <row r="89" spans="1:10" ht="13.5" customHeight="1">
+        <v>35</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="28.8" customHeight="1">
       <c r="B89" s="6" t="s">
         <v>35</v>
       </c>
@@ -2028,396 +2048,393 @@
         <v>50</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="J89" s="1"/>
-    </row>
-    <row r="90" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A90" s="7" t="s">
-        <v>95</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A90" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C90" s="7"/>
       <c r="I90" s="8"/>
-      <c r="J90" s="1"/>
     </row>
     <row r="91" spans="1:10" ht="13.5" customHeight="1">
       <c r="B91" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="28.2" customHeight="1">
+        <v>111</v>
+      </c>
+      <c r="J91" s="1"/>
+    </row>
+    <row r="92" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A92" s="7" t="s">
+        <v>95</v>
+      </c>
       <c r="B92" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I92" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B93" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I93" s="8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A94" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="C92" s="7"/>
+      <c r="I92" s="8"/>
+      <c r="J92" s="1"/>
+    </row>
+    <row r="93" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A93" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B93" s="6"/>
+      <c r="C93" s="7"/>
+      <c r="I93" s="8"/>
+      <c r="J93" s="1"/>
+    </row>
+    <row r="94" spans="1:10" ht="13.5" customHeight="1">
       <c r="B94" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="J94" s="1"/>
-    </row>
-    <row r="95" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A95" s="1"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="28.2" customHeight="1">
       <c r="B95" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="J95" s="1"/>
-    </row>
-    <row r="96" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A96" s="1"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="28.2" customHeight="1">
       <c r="B96" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C96" s="9" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="28.2" customHeight="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A97" s="1"/>
       <c r="B97" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C97" s="1"/>
       <c r="I97" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="13.5" customHeight="1">
+        <v>117</v>
+      </c>
+      <c r="J97" s="1"/>
+    </row>
+    <row r="98" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A98" s="1"/>
       <c r="B98" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C98" s="1"/>
       <c r="I98" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A99" s="5" t="s">
-        <v>21</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="J98" s="1"/>
+    </row>
+    <row r="99" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A99" s="1"/>
       <c r="B99" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I99" s="8"/>
-    </row>
-    <row r="100" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A100" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>125</v>
+        <v>35</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B100" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="C100" s="1"/>
-      <c r="D100" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="I100" s="8"/>
-    </row>
-    <row r="101" spans="1:9" ht="13.2" customHeight="1">
+      <c r="I100" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="13.5" customHeight="1">
       <c r="B101" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C101" s="1"/>
       <c r="I101" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A102" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I102" s="8"/>
+    </row>
+    <row r="103" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A103" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C103" s="1"/>
+      <c r="D103" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="I103" s="8"/>
+    </row>
+    <row r="104" spans="1:10" ht="13.2" customHeight="1">
+      <c r="B104" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C104" s="1"/>
+      <c r="I104" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="27.6" customHeight="1">
-      <c r="B102" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C102" s="7" t="s">
+    <row r="105" spans="1:10" ht="13.2" customHeight="1">
+      <c r="A105" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C105" s="1"/>
+      <c r="I105" s="8"/>
+    </row>
+    <row r="106" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B106" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C106" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="I102" s="8" t="s">
+      <c r="I106" s="8" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B103" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C103" s="7" t="s">
+    <row r="107" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B107" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C107" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="I103" s="10" t="s">
+      <c r="I107" s="10" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="30" customHeight="1">
-      <c r="A104" s="1"/>
-      <c r="B104" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C104" s="6" t="s">
+    <row r="108" spans="1:10" ht="30" customHeight="1">
+      <c r="A108" s="1"/>
+      <c r="B108" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C108" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="I104" s="10" t="s">
+      <c r="I108" s="10" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B105" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C105" s="6" t="s">
+    <row r="109" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B109" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C109" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="I105" s="8" t="s">
+      <c r="I109" s="8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B106" s="6" t="s">
+    <row r="110" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B110" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C106" s="1"/>
-      <c r="I106" s="8" t="s">
+      <c r="C110" s="1"/>
+      <c r="I110" s="8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B107" s="6" t="s">
+    <row r="111" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B111" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C107" s="1"/>
-      <c r="I107" s="8" t="s">
+      <c r="C111" s="1"/>
+      <c r="I111" s="8" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="28.2" customHeight="1">
-      <c r="B108" s="6" t="s">
+    <row r="112" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B112" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C108" s="1"/>
-      <c r="I108" s="8" t="s">
+      <c r="C112" s="1"/>
+      <c r="I112" s="8" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A109" s="1"/>
-      <c r="B109" s="6" t="s">
+    <row r="113" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A113" s="1"/>
+      <c r="B113" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I109" s="8" t="s">
+      <c r="I113" s="8" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A110" s="9" t="s">
+    <row r="114" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A114" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B114" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I110" s="8" t="s">
+      <c r="I114" s="8" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A111" s="1" t="s">
+    <row r="115" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A115" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I111" s="1"/>
-    </row>
-    <row r="112" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B112" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C112" s="9" t="s">
+      <c r="I115" s="1"/>
+    </row>
+    <row r="116" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A116" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="I116" s="1"/>
+    </row>
+    <row r="117" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B117" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C117" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I112" s="8" t="s">
+      <c r="I117" s="8" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A113" s="7" t="s">
+    <row r="118" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A118" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="6" t="s">
+      <c r="B118" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C113" s="9"/>
-      <c r="I113" s="8"/>
-    </row>
-    <row r="114" spans="1:9" ht="13.2" customHeight="1">
-      <c r="A114" s="5" t="s">
+      <c r="C118" s="9"/>
+      <c r="I118" s="8"/>
+    </row>
+    <row r="119" spans="1:9" ht="13.2" customHeight="1">
+      <c r="A119" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B114" s="6" t="s">
+      <c r="B119" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C114" s="9"/>
-      <c r="I114" s="8"/>
-    </row>
-    <row r="115" spans="1:9" ht="13.2" customHeight="1">
-      <c r="A115" s="5"/>
-      <c r="B115" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C115" s="6" t="s">
+      <c r="C119" s="9"/>
+      <c r="I119" s="8"/>
+    </row>
+    <row r="120" spans="1:9" ht="13.2" customHeight="1">
+      <c r="A120" s="5"/>
+      <c r="B120" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C120" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="I115" s="8"/>
-    </row>
-    <row r="116" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A116" s="1"/>
-      <c r="B116" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I116" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A117" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="I117" s="8"/>
-    </row>
-    <row r="118" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A118" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C118" s="1"/>
-      <c r="D118" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="I118" s="8"/>
-    </row>
-    <row r="119" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A119" s="1"/>
-      <c r="B119" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H119" s="1"/>
-      <c r="I119" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B120" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C120" s="1"/>
-      <c r="I120" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I120" s="8"/>
+    </row>
+    <row r="121" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A121" s="1"/>
       <c r="B121" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C121" s="1"/>
       <c r="I121" s="8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" ht="13.5" customHeight="1">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A122" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="B122" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="I122" s="8"/>
+    </row>
+    <row r="123" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A123" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C123" s="1"/>
+      <c r="D123" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="I123" s="8"/>
+    </row>
+    <row r="124" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A124" s="1"/>
+      <c r="B124" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C122" s="1"/>
-      <c r="I122" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A123" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C123" s="1"/>
-      <c r="I123" s="8"/>
-    </row>
-    <row r="124" spans="1:9" ht="30" customHeight="1">
-      <c r="B124" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>50</v>
-      </c>
+      <c r="H124" s="1"/>
       <c r="I124" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" ht="30" customHeight="1">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="28.8" customHeight="1">
       <c r="B125" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>50</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C125" s="1"/>
       <c r="I125" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="13.5" customHeight="1">
       <c r="B126" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>50</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C126" s="1"/>
       <c r="I126" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A127" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="B127" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C127" s="1"/>
       <c r="I127" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A128" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B128" s="1"/>
+      <c r="A128" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="C128" s="1"/>
-      <c r="I128" s="1"/>
-    </row>
-    <row r="129" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I128" s="8"/>
+    </row>
+    <row r="129" spans="1:10" ht="30" customHeight="1">
       <c r="B129" s="6" t="s">
         <v>35</v>
       </c>
@@ -2425,173 +2442,200 @@
         <v>50</v>
       </c>
       <c r="I129" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="30" customHeight="1">
+      <c r="B130" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B131" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A132" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A133" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="I133" s="1"/>
+    </row>
+    <row r="134" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B134" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I134" s="8" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A130" s="9" t="s">
+    <row r="135" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A135" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B135" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C130" s="1"/>
-      <c r="I130" s="8" t="s">
+      <c r="C135" s="1"/>
+      <c r="I135" s="8" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A131" s="1" t="s">
+    <row r="136" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A136" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="I131" s="1"/>
-    </row>
-    <row r="132" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B132" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C132" s="6" t="s">
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="I136" s="1"/>
+    </row>
+    <row r="137" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B137" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C137" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I132" s="8" t="s">
+      <c r="I137" s="8" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A133" s="7" t="s">
+    <row r="138" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A138" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B133" s="6" t="s">
+      <c r="B138" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C133" s="6"/>
-      <c r="I133" s="8"/>
-    </row>
-    <row r="134" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A134" s="7"/>
-      <c r="B134" s="6"/>
-      <c r="C134" s="6"/>
-      <c r="I134" s="8"/>
-    </row>
-    <row r="135" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A135" s="5" t="s">
+      <c r="C138" s="6"/>
+      <c r="I138" s="8"/>
+    </row>
+    <row r="139" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A139" s="7"/>
+      <c r="B139" s="6"/>
+      <c r="C139" s="6"/>
+      <c r="I139" s="8"/>
+    </row>
+    <row r="140" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A140" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B135" s="6" t="s">
+      <c r="B140" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="C135" s="6"/>
-      <c r="I135" s="8"/>
-    </row>
-    <row r="136" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A136" s="1"/>
-      <c r="B136" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C136" s="6" t="s">
+      <c r="C140" s="6"/>
+      <c r="I140" s="8"/>
+    </row>
+    <row r="141" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A141" s="1"/>
+      <c r="B141" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C141" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="I136" s="8" t="s">
+      <c r="I141" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="J136" s="1"/>
-    </row>
-    <row r="137" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A137" s="5" t="s">
+      <c r="J141" s="1"/>
+    </row>
+    <row r="142" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A142" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B137" s="6" t="s">
+      <c r="B142" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="I137" s="8"/>
-      <c r="J137" s="1"/>
-    </row>
-    <row r="138" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A138" s="6" t="s">
+      <c r="I142" s="8"/>
+      <c r="J142" s="1"/>
+    </row>
+    <row r="143" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A143" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B138" s="7" t="s">
+      <c r="B143" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C138" s="1"/>
-      <c r="D138" s="6" t="s">
+      <c r="C143" s="1"/>
+      <c r="D143" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="I138" s="8"/>
-      <c r="J138" s="1"/>
-    </row>
-    <row r="139" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A139" s="1"/>
-      <c r="B139" s="1"/>
-      <c r="I139" s="8" t="s">
+      <c r="I143" s="8"/>
+      <c r="J143" s="1"/>
+    </row>
+    <row r="144" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A144" s="1"/>
+      <c r="B144" s="1"/>
+      <c r="I144" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="J139" s="1"/>
-    </row>
-    <row r="140" spans="1:10" ht="30" customHeight="1">
-      <c r="A140" s="1"/>
-      <c r="I140" s="8" t="s">
+      <c r="J144" s="1"/>
+    </row>
+    <row r="145" spans="1:10" ht="30" customHeight="1">
+      <c r="A145" s="1"/>
+      <c r="I145" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="J140" s="1"/>
-    </row>
-    <row r="141" spans="1:10" ht="30" customHeight="1">
-      <c r="A141" s="5" t="s">
+      <c r="J145" s="1"/>
+    </row>
+    <row r="146" spans="1:10" ht="30" customHeight="1">
+      <c r="A146" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B141" s="6" t="s">
+      <c r="B146" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="I141" s="8"/>
-      <c r="J141" s="1"/>
-    </row>
-    <row r="142" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B142" s="1"/>
-      <c r="C142" s="1"/>
-      <c r="I142" s="8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A143" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="B143" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G143">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A144" s="1"/>
-    </row>
-    <row r="145" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B145" s="1"/>
-      <c r="C145" s="1"/>
-      <c r="I145" s="1"/>
-    </row>
-    <row r="146" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B146" s="1"/>
-      <c r="C146" s="1"/>
-      <c r="I146" s="1"/>
-    </row>
-    <row r="147" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I146" s="8"/>
+      <c r="J146" s="1"/>
+    </row>
+    <row r="147" spans="1:10" ht="28.8" customHeight="1">
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
-      <c r="I147" s="1"/>
+      <c r="I147" s="8" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="148" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A148" s="1"/>
-      <c r="B148" s="1"/>
+      <c r="A148" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G148">
+        <v>1</v>
+      </c>
     </row>
     <row r="149" spans="1:10" ht="13.5" customHeight="1">
       <c r="A149" s="1"/>
-      <c r="B149" s="1"/>
-      <c r="I149" s="1"/>
-      <c r="J149" s="1"/>
     </row>
     <row r="150" spans="1:10" ht="13.5" customHeight="1">
       <c r="B150" s="1"/>
@@ -2604,64 +2648,84 @@
       <c r="I151" s="1"/>
     </row>
     <row r="152" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A152" s="1"/>
       <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="I152" s="1"/>
     </row>
     <row r="153" spans="1:10" ht="13.5" customHeight="1">
       <c r="A153" s="1"/>
+      <c r="B153" s="1"/>
     </row>
     <row r="154" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A154" s="1"/>
+      <c r="B154" s="1"/>
       <c r="I154" s="1"/>
+      <c r="J154" s="1"/>
     </row>
     <row r="155" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A155" s="1"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="I155" s="1"/>
     </row>
     <row r="156" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A156" s="1"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
+      <c r="I156" s="1"/>
     </row>
     <row r="157" spans="1:10" ht="13.5" customHeight="1">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
-      <c r="H157" s="1"/>
-      <c r="I157" s="1"/>
     </row>
     <row r="158" spans="1:10" ht="13.5" customHeight="1">
       <c r="A158" s="1"/>
-      <c r="H158" s="1"/>
-      <c r="I158" s="1"/>
     </row>
     <row r="159" spans="1:10" ht="13.5" customHeight="1">
       <c r="I159" s="1"/>
     </row>
     <row r="160" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I160" s="1"/>
-    </row>
-    <row r="161" spans="9:9" ht="13.5" customHeight="1">
-      <c r="I161" s="1"/>
-    </row>
-    <row r="162" spans="9:9" ht="13.5" customHeight="1">
+      <c r="A160" s="1"/>
+    </row>
+    <row r="161" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A161" s="1"/>
+    </row>
+    <row r="162" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A162" s="1"/>
+      <c r="B162" s="1"/>
+      <c r="H162" s="1"/>
       <c r="I162" s="1"/>
     </row>
-    <row r="163" spans="9:9" ht="13.5" customHeight="1">
+    <row r="163" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A163" s="1"/>
+      <c r="H163" s="1"/>
       <c r="I163" s="1"/>
     </row>
-    <row r="164" spans="9:9" ht="13.5" customHeight="1">
+    <row r="164" spans="1:9" ht="13.5" customHeight="1">
       <c r="I164" s="1"/>
     </row>
-    <row r="165" spans="9:9" ht="13.5" customHeight="1">
+    <row r="165" spans="1:9" ht="13.5" customHeight="1">
       <c r="I165" s="1"/>
     </row>
-    <row r="166" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="167" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="168" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="169" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="170" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="171" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="172" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="173" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="174" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="175" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="176" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="166" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I166" s="1"/>
+    </row>
+    <row r="167" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I167" s="1"/>
+    </row>
+    <row r="168" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I168" s="1"/>
+    </row>
+    <row r="169" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I169" s="1"/>
+    </row>
+    <row r="170" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I170" s="1"/>
+    </row>
+    <row r="171" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="172" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="173" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="174" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="175" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="176" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="177" ht="13.5" customHeight="1"/>
     <row r="178" ht="13.5" customHeight="1"/>
     <row r="179" ht="13.5" customHeight="1"/>
@@ -2702,19 +2766,19 @@
     <row r="214" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="215" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="216" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="217" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A217" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
+    <row r="217" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="218" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="219" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="220" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="221" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="222" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="222" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A222" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
     <row r="223" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="224" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="225" ht="13.5" customHeight="1"/>
@@ -3577,6 +3641,11 @@
     <row r="1082" ht="13.5" customHeight="1"/>
     <row r="1083" ht="13.5" customHeight="1"/>
     <row r="1084" ht="13.5" customHeight="1"/>
+    <row r="1085" ht="13.5" customHeight="1"/>
+    <row r="1086" ht="13.5" customHeight="1"/>
+    <row r="1087" ht="13.5" customHeight="1"/>
+    <row r="1088" ht="13.5" customHeight="1"/>
+    <row r="1089" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
